--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1159,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="19" min="1" max="1"/>
@@ -1330,7 +1330,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A6,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A6,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="M7" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A7,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A7,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -1464,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A8,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A8,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A9,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A9,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -1598,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A10,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A10,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N10" s="11" t="inlineStr">
@@ -1665,7 +1665,7 @@
         <v>3</v>
       </c>
       <c r="M11" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A11,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A11,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -1732,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="M12" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A12,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A12,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -1799,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A13,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A13,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N13" s="13" t="inlineStr">
@@ -1866,7 +1866,7 @@
         <v>3</v>
       </c>
       <c r="M14" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A14,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A14,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N14" s="11" t="inlineStr">
@@ -1933,7 +1933,7 @@
         <v>4</v>
       </c>
       <c r="M15" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A15,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A15,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N15" s="13" t="inlineStr">
@@ -2000,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="M16" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A16,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A16,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -2067,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="M17" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A17,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A17,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N17" s="13" t="inlineStr">
@@ -2134,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A18,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A18,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -2201,7 +2201,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A19,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A19,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N19" s="13" t="inlineStr">
@@ -2268,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="M20" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A20,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A20,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -2335,7 +2335,7 @@
         <v>3</v>
       </c>
       <c r="M21" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A21,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A21,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N21" s="13" t="inlineStr">
@@ -2402,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A22,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A22,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>4</v>
       </c>
       <c r="M23" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A23,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A23,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N23" s="13" t="inlineStr">
@@ -2536,7 +2536,7 @@
         <v>3</v>
       </c>
       <c r="M24" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A24,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A24,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -2603,7 +2603,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A25,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A25,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N25" s="13" t="inlineStr">
@@ -2670,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="M26" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A26,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A26,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -2741,7 +2741,7 @@
         <v>3</v>
       </c>
       <c r="M27" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A27,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A27,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N27" s="11" t="inlineStr">
@@ -2812,7 +2812,7 @@
         <v>3</v>
       </c>
       <c r="M28" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A28,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A28,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N28" s="11" t="inlineStr">
@@ -2883,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="M29" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A29,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A29,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -2954,7 +2954,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A30,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A30,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N30" s="11" t="inlineStr">
@@ -2965,7 +2965,7 @@
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Parte móvil + SMTP (T-6301). La historia web sigue en el Sprint 1. Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v>2</v>
       </c>
       <c r="M31" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A31,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A31,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -3096,7 +3096,7 @@
         <v>3</v>
       </c>
       <c r="M32" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A32,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A32,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N32" s="11" t="inlineStr">
@@ -3107,7 +3107,7 @@
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="M33" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A33,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A33,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         <v>3</v>
       </c>
       <c r="M34" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A34,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A34,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -3249,7 +3249,7 @@
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>4</v>
       </c>
       <c r="M35" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A35,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A35,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -3320,7 +3320,7 @@
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
         <v>2</v>
       </c>
       <c r="M36" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A36,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A36,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -3391,7 +3391,7 @@
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         <v>4</v>
       </c>
       <c r="M37" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A37,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A37,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N37" s="11" t="inlineStr">
@@ -3522,7 +3522,7 @@
         <v>2</v>
       </c>
       <c r="M38" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A38,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A38,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N38" s="11" t="inlineStr">
@@ -3593,7 +3593,7 @@
         <v>3</v>
       </c>
       <c r="M39" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A39,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A39,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N39" s="11" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
         <v>3</v>
       </c>
       <c r="M40" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A40,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A40,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N40" s="11" t="inlineStr">
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="M41" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A41,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A41,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -3810,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="M42" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A42,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A42,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N42" s="11" t="inlineStr">
@@ -3881,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="M43" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A43,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A43,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N43" s="11" t="inlineStr">
@@ -3952,7 +3952,7 @@
         <v>2</v>
       </c>
       <c r="M44" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A44,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A44,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N44" s="11" t="inlineStr">
@@ -4023,7 +4023,7 @@
         <v>2</v>
       </c>
       <c r="M45" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A45,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A45,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N45" s="11" t="inlineStr">
@@ -4094,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="M46" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A46,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A46,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N46" s="11" t="inlineStr">
@@ -4165,12 +4165,12 @@
         <v>5</v>
       </c>
       <c r="M47" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A47,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A47,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O47" s="12" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A48,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A48,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N48" s="11" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
         <v>4</v>
       </c>
       <c r="M49" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A49,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A49,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N49" s="11" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
         <v>3</v>
       </c>
       <c r="M50" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A50,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A50,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N50" s="11" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
         <v>3</v>
       </c>
       <c r="M51" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A51,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A51,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N51" s="11" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
         <v>2</v>
       </c>
       <c r="M52" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A52,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A52,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N52" s="11" t="inlineStr">
@@ -4611,7 +4611,7 @@
         <v>4</v>
       </c>
       <c r="M53" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A53,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A53,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N53" s="11" t="inlineStr">
@@ -4682,12 +4682,12 @@
         <v>5</v>
       </c>
       <c r="M54" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A54,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A54,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O54" s="12" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
         <v>3</v>
       </c>
       <c r="M55" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A55,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A55,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N55" s="11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
         <v>3</v>
       </c>
       <c r="M56" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A56,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A56,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O56" s="12" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
         <v>4</v>
       </c>
       <c r="M57" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A57,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A57,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -4974,12 +4974,12 @@
         <v>3</v>
       </c>
       <c r="M58" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A58,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A58,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O58" s="12" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
         <v>3</v>
       </c>
       <c r="M59" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A59,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A59,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O59" s="12" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5124,12 @@
         <v>3</v>
       </c>
       <c r="M60" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A60,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A60,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O60" s="12" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5199,12 @@
         <v>3</v>
       </c>
       <c r="M61" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A61,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A61,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O61" s="12" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
         <v>4</v>
       </c>
       <c r="M62" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A62,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A62,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N62" s="11" t="inlineStr">
@@ -5345,7 +5345,7 @@
         <v>3</v>
       </c>
       <c r="M63" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A63,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A63,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N63" s="11" t="inlineStr">
@@ -5416,7 +5416,7 @@
         <v>4</v>
       </c>
       <c r="M64" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A64,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A64,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N64" s="11" t="inlineStr">
@@ -5427,7 +5427,7 @@
       <c r="O64" s="12" t="n"/>
       <c r="P64" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131.</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="M65" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A65,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A65,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N65" s="11" t="inlineStr">
@@ -5498,7 +5498,7 @@
       <c r="O65" s="12" t="n"/>
       <c r="P65" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
         <v>4</v>
       </c>
       <c r="M66" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A66,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A66,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N66" s="11" t="inlineStr">
@@ -5569,7 +5569,7 @@
       <c r="O66" s="12" t="n"/>
       <c r="P66" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
         <v>3</v>
       </c>
       <c r="M67" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A67,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A67,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N67" s="11" t="inlineStr">
@@ -5700,7 +5700,7 @@
         <v>2</v>
       </c>
       <c r="M68" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A68,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A68,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N68" s="11" t="inlineStr">
@@ -5771,7 +5771,7 @@
         <v>2</v>
       </c>
       <c r="M69" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A69,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A69,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N69" s="11" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="O69" s="12" t="n"/>
       <c r="P69" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
         <v>3</v>
       </c>
       <c r="M70" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A70,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A70,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N70" s="11" t="inlineStr">
@@ -5853,7 +5853,7 @@
       <c r="O70" s="12" t="n"/>
       <c r="P70" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="M71" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$508,$A71,Tareas!$F$6:$F$508)</f>
+        <f>SUMIF(Tareas!$B$6:$B$513,$A71,Tareas!$F$6:$F$513)</f>
         <v/>
       </c>
       <c r="N71" s="11" t="inlineStr">
@@ -5925,6 +5925,77 @@
       <c r="P71" s="12" t="inlineStr">
         <is>
           <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>HU-011</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>EP-02</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Administrar las plantas del cliente</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>administrador del cliente</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>registrar las plantas o instalaciones de la empresa</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>poder separar la operación por ubicación física</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>Web (infraestructura)</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>HU-010</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" s="11">
+        <f>SUMIF(Tareas!$B$6:$B$513,$A72,Tareas!$F$6:$F$513)</f>
+        <v/>
+      </c>
+      <c r="N72" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="O72" s="12" t="n"/>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>Solo la tarea de infraestructura (clave de Google Maps). La historia sigue en el Sprint 1.</t>
         </is>
       </c>
     </row>
@@ -5978,7 +6049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J508"/>
+  <dimension ref="A1:J513"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="19" min="1" max="1"/>
@@ -14459,7 +14530,7 @@
       <c r="I205" s="11" t="n"/>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -14505,7 +14576,7 @@
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -14551,7 +14622,7 @@
       <c r="I207" s="11" t="n"/>
       <c r="J207" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14668,7 @@
       <c r="I208" s="11" t="n"/>
       <c r="J208" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14714,7 @@
       <c r="I209" s="11" t="n"/>
       <c r="J209" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14760,7 @@
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14806,7 @@
       <c r="I211" s="11" t="n"/>
       <c r="J211" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 1 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -14821,15 +14892,13 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I213" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="n"/>
       <c r="J213" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. API_SEL_APP_SABANA_DATOS (bloques 1-13), acotado a las plantas del usuario</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_SEL_APP_SABANA_DATOS (bloques 1-13), acotado a las plantas del usuario</t>
         </is>
       </c>
     </row>
@@ -14915,15 +14984,13 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I215" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="n"/>
       <c r="J215" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Datos de Hamburgo: 31 órdenes abiertas, pautas pendientes, 3 posiciones</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Datos de Hamburgo: 31 órdenes abiertas, pautas pendientes, 3 posiciones</t>
         </is>
       </c>
     </row>
@@ -14963,15 +15030,13 @@
       </c>
       <c r="H216" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I216" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I216" s="11" t="n"/>
       <c r="J216" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. GET /sincronizacion y GET /sincronizacion/{tipo}?desde=</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /sincronizacion y GET /sincronizacion/{tipo}?desde=</t>
         </is>
       </c>
     </row>
@@ -15057,15 +15122,13 @@
       </c>
       <c r="H218" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I218" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I218" s="11" t="n"/>
       <c r="J218" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. FNC_SUSCRIPCION_VIGENTE en ApiBase responde 402 (HU-193)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. FNC_SUSCRIPCION_VIGENTE en ApiBase responde 402 (HU-193)</t>
         </is>
       </c>
     </row>
@@ -15105,15 +15168,13 @@
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I219" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="n"/>
       <c r="J219" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. sincronizacion_screen con barra por bloque</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. sincronizacion_screen con barra por bloque</t>
         </is>
       </c>
     </row>
@@ -15153,15 +15214,13 @@
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I220" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="n"/>
       <c r="J220" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. OutboxService + CacheDatos en SQLite</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OutboxService + CacheDatos en SQLite</t>
         </is>
       </c>
     </row>
@@ -15201,15 +15260,13 @@
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I221" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I221" s="11" t="n"/>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Corte a medias: el bloque fallido se marca y el corte no se guarda hasta que todos lleguen; el outbox reintenta por uuid</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Corte a medias: el bloque fallido se marca y el corte no se guarda hasta que todos lleguen; el outbox reintenta por uuid</t>
         </is>
       </c>
     </row>
@@ -15249,15 +15306,13 @@
       </c>
       <c r="H222" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I222" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I222" s="11" t="n"/>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. ExigirUsuario/ExigirCliente en el controller; el cliente sale del token</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. ExigirUsuario/ExigirCliente en el controller; el cliente sale del token</t>
         </is>
       </c>
     </row>
@@ -15297,15 +15352,13 @@
       </c>
       <c r="H223" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I223" s="11" t="n">
-        <v>1.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I223" s="11" t="n"/>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Evidencia S2 HU-150 #1-#3 (Swagger)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Evidencia S2 HU-150 #1-#3 (Swagger)</t>
         </is>
       </c>
     </row>
@@ -15345,15 +15398,13 @@
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I224" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I224" s="11" t="n"/>
       <c r="J224" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Swagger documentado; decisiones en SIGMA_APP_DATOS_SINCRONIZACION.md y checklist §10.17</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Swagger documentado; decisiones en SIGMA_APP_DATOS_SINCRONIZACION.md y checklist §10.17</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15450,7 @@
       <c r="I225" s="11" t="n"/>
       <c r="J225" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15496,7 @@
       <c r="I226" s="11" t="n"/>
       <c r="J226" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15542,7 @@
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15531,15 +15582,13 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="n"/>
       <c r="J228" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. API_INS_ACTIVO_MEDIDOR_LECTURA (141) + salto no razonable → pendiente de revisión y alerta (BD/235)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_INS_ACTIVO_MEDIDOR_LECTURA (141) + salto no razonable → pendiente de revisión y alerta (BD/235)</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15634,7 @@
       <c r="I229" s="11" t="n"/>
       <c r="J229" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15680,7 @@
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15671,15 +15720,13 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I231" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I231" s="11" t="n"/>
       <c r="J231" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. MED-33-H con máximo diario 24 h; lecturas de ronda y salto de 400 h</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MED-33-H con máximo diario 24 h; lecturas de ronda y salto de 400 h</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15772,7 @@
       <c r="I232" s="11" t="n"/>
       <c r="J232" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15765,15 +15812,13 @@
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I233" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="n"/>
       <c r="J233" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. GET /medidores/{id} y GET /medidores/{id}/lecturas (bloque 203)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /medidores/{id} y GET /medidores/{id}/lecturas (bloque 203)</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15864,7 @@
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -15859,15 +15904,13 @@
       </c>
       <c r="H235" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I235" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I235" s="11" t="n"/>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. CapturaScreen desde el medidor; cuerpo con los nombres del DTO (defecto corregido 16-09)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. CapturaScreen desde el medidor; cuerpo con los nombres del DTO (defecto corregido 16-09)</t>
         </is>
       </c>
     </row>
@@ -15907,15 +15950,13 @@
       </c>
       <c r="H236" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I236" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I236" s="11" t="n"/>
       <c r="J236" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. REGISTRAR LECTURA en la API; medidor validado contra el cliente del token</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. REGISTRAR LECTURA en la API; medidor validado contra el cliente del token</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16002,7 @@
       <c r="I237" s="11" t="n"/>
       <c r="J237" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16048,7 @@
       <c r="I238" s="11" t="n"/>
       <c r="J238" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16094,7 @@
       <c r="I239" s="11" t="n"/>
       <c r="J239" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16140,7 @@
       <c r="I240" s="11" t="n"/>
       <c r="J240" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16139,15 +16180,13 @@
       </c>
       <c r="H241" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I241" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I241" s="11" t="n"/>
       <c r="J241" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. UPD_ACTIVO_POSICION_OCUPAR idempotente por aph_uuid (BD/231)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. UPD_ACTIVO_POSICION_OCUPAR idempotente por aph_uuid (BD/231)</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16232,7 @@
       <c r="I242" s="11" t="n"/>
       <c r="J242" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16233,15 +16272,13 @@
       </c>
       <c r="H243" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I243" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I243" s="11" t="n"/>
       <c r="J243" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Bloque 11 POSICIONES de la sábana (BD/232); GET /sincronizacion/11</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Bloque 11 POSICIONES de la sábana (BD/232); GET /sincronizacion/11</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16324,7 @@
       <c r="I244" s="11" t="n"/>
       <c r="J244" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16327,15 +16364,13 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I245" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="n"/>
       <c r="J245" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. El middleware de suscripción (FNC_SUSCRIPCION_VIGENTE) ya cubre /escaneo y /posiciones</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. El middleware de suscripción (FNC_SUSCRIPCION_VIGENTE) ya cubre /escaneo y /posiciones</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16416,7 @@
       <c r="I246" s="11" t="n"/>
       <c r="J246" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16421,15 +16456,13 @@
       </c>
       <c r="H247" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I247" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I247" s="11" t="n"/>
       <c r="J247" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. HojaOcuparPosicion encola con uuid en el outbox; escaneo POS- en escaneo_screen</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. HojaOcuparPosicion encola con uuid en el outbox; escaneo POS- en escaneo_screen</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16508,7 @@
       <c r="I248" s="11" t="n"/>
       <c r="J248" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16554,7 @@
       <c r="I249" s="11" t="n"/>
       <c r="J249" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16600,7 @@
       <c r="I250" s="11" t="n"/>
       <c r="J250" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16646,7 @@
       <c r="I251" s="11" t="n"/>
       <c r="J251" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16692,7 @@
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16699,15 +16732,13 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I253" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I253" s="11" t="n"/>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. API_INS_ACTIVO_MEDICION: equivalente en la unidad de la variable, comentario obligatorio fuera de umbral y alerta (BD/235)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_INS_ACTIVO_MEDICION: equivalente en la unidad de la variable, comentario obligatorio fuera de umbral y alerta (BD/235)</t>
         </is>
       </c>
     </row>
@@ -16753,7 +16784,7 @@
       <c r="I254" s="11" t="n"/>
       <c r="J254" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16799,7 +16830,7 @@
       <c r="I255" s="11" t="n"/>
       <c r="J255" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16839,15 +16870,13 @@
       </c>
       <c r="H256" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I256" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I256" s="11" t="n"/>
       <c r="J256" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. Variable Presión en bar de ACT-36; mediciones en psi y bar</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Variable Presión en bar de ACT-36; mediciones en psi y bar</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16922,7 @@
       <c r="I257" s="11" t="n"/>
       <c r="J257" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -16933,15 +16962,13 @@
       </c>
       <c r="H258" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I258" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I258" s="11" t="n"/>
       <c r="J258" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. GET /captura/mediciones se cubre con la serie web (BD/233); detalle por Alerta</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /captura/mediciones se cubre con la serie web (BD/233); detalle por Alerta</t>
         </is>
       </c>
     </row>
@@ -16987,7 +17014,7 @@
       <c r="I259" s="11" t="n"/>
       <c r="J259" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17027,15 +17054,13 @@
       </c>
       <c r="H260" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I260" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I260" s="11" t="n"/>
       <c r="J260" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. CapturaScreen elige la variable (sábana) y pide comentario fuera de umbral</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. CapturaScreen elige la variable (sábana) y pide comentario fuera de umbral</t>
         </is>
       </c>
     </row>
@@ -17075,15 +17100,13 @@
       </c>
       <c r="H261" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I261" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I261" s="11" t="n"/>
       <c r="J261" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. REGISTRAR MEDICION en la API; variable validada contra el cliente del token</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. REGISTRAR MEDICION en la API; variable validada contra el cliente del token</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17152,7 @@
       <c r="I262" s="11" t="n"/>
       <c r="J262" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17175,7 +17198,7 @@
       <c r="I263" s="11" t="n"/>
       <c r="J263" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17244,7 @@
       <c r="I264" s="11" t="n"/>
       <c r="J264" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17261,15 +17284,13 @@
       </c>
       <c r="H265" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I265" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I265" s="11" t="n"/>
       <c r="J265" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 2 como MVP de la app; se formaliza en el Sprint 6. POST /activo-estados con motivo obligatorio y cierre del periodo anterior (evidencia HU-038)</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /activo-estados con motivo obligatorio y cierre del periodo anterior (evidencia HU-038)</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17382,7 @@
       <c r="I267" s="11" t="n"/>
       <c r="J267" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17428,7 @@
       <c r="I268" s="11" t="n"/>
       <c r="J268" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17493,15 +17514,13 @@
       </c>
       <c r="H270" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I270" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I270" s="11" t="n"/>
       <c r="J270" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 3 como MVP de la app; se formaliza en el Sprint 6. Ya existia como la sabana: GET /sincronizacion (manifiesto) y GET /sincronizacion/{bloque}?desde=, acotada a las plantas del usuario por API_SEL_APP_SABANA_DATOS (bloques 140-234).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existia como la sabana: GET /sincronizacion (manifiesto) y GET /sincronizacion/{bloque}?desde=, acotada a las plantas del usuario por API_SEL_APP_SABANA_DATOS (bloques 140-234).</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17566,7 @@
       <c r="I271" s="11" t="n"/>
       <c r="J271" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17587,15 +17606,13 @@
       </c>
       <c r="H272" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I272" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I272" s="11" t="n"/>
       <c r="J272" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 3 como MVP de la app; se formaliza en el Sprint 6. SuscripcionHandler en el pipeline de Web API: con cliente en el token y PUEDE_OPERAR=0 (SEL_SUSCRIPCION_ESTADO_CLIENTE -&gt; FNC_SUSCRIPCION_VIGENTE) responde 402 con el cuerpo estandar; cache 60 s por cliente; registra en Suscripcion_Bloqueo_Log origen API; exentas /sesion, /cliente-usuarios, /mi-perfil.</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. SuscripcionHandler en el pipeline de Web API: con cliente en el token y PUEDE_OPERAR=0 (SEL_SUSCRIPCION_ESTADO_CLIENTE -&gt; FNC_SUSCRIPCION_VIGENTE) responde 402 con el cuerpo estandar; cache 60 s por cliente; registra en Suscripcion_Bloqueo_Log origen API; exentas /sesion, /cliente-usuarios, /mi-perfil.</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17658,7 @@
       <c r="I273" s="11" t="n"/>
       <c r="J273" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17687,7 +17704,7 @@
       <c r="I274" s="11" t="n"/>
       <c r="J274" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17733,7 +17750,7 @@
       <c r="I275" s="11" t="n"/>
       <c r="J275" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17773,15 +17790,13 @@
       </c>
       <c r="H276" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I276" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I276" s="11" t="n"/>
       <c r="J276" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 3 como MVP de la app; se formaliza en el Sprint 6. La API valida permiso con ExigirPermiso/ExigirCliente y el cliente sale del token, nunca de un parametro; la sabana filtra por las plantas del usuario.</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. La API valida permiso con ExigirPermiso/ExigirCliente y el cliente sale del token, nunca de un parametro; la sabana filtra por las plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17842,7 @@
       <c r="I277" s="11" t="n"/>
       <c r="J277" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17888,7 @@
       <c r="I278" s="11" t="n"/>
       <c r="J278" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17919,7 +17934,7 @@
       <c r="I279" s="11" t="n"/>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -17965,7 +17980,7 @@
       <c r="I280" s="11" t="n"/>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18026,7 @@
       <c r="I281" s="11" t="n"/>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18072,7 @@
       <c r="I282" s="11" t="n"/>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18118,7 @@
       <c r="I283" s="11" t="n"/>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18149,7 +18164,7 @@
       <c r="I284" s="11" t="n"/>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18210,7 @@
       <c r="I285" s="11" t="n"/>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18256,7 @@
       <c r="I286" s="11" t="n"/>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18281,15 +18296,13 @@
       </c>
       <c r="H287" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I287" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I287" s="11" t="n"/>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18329,15 +18342,13 @@
       </c>
       <c r="H288" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I288" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I288" s="11" t="n"/>
       <c r="J288" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18377,15 +18388,13 @@
       </c>
       <c r="H289" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I289" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I289" s="11" t="n"/>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18425,15 +18434,13 @@
       </c>
       <c r="H290" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I290" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I290" s="11" t="n"/>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18473,15 +18480,13 @@
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I291" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I291" s="11" t="n"/>
       <c r="J291" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18521,15 +18526,13 @@
       </c>
       <c r="H292" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I292" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I292" s="11" t="n"/>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18569,15 +18572,13 @@
       </c>
       <c r="H293" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I293" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I293" s="11" t="n"/>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Middleware de suscripción ya existía en ApiBase (FNC_SUSCRIPCION_VIGENTE).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Middleware de suscripción ya existía en ApiBase (FNC_SUSCRIPCION_VIGENTE).</t>
         </is>
       </c>
     </row>
@@ -18617,15 +18618,13 @@
       </c>
       <c r="H294" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I294" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I294" s="11" t="n"/>
       <c r="J294" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18665,15 +18664,13 @@
       </c>
       <c r="H295" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I295" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I295" s="11" t="n"/>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18713,15 +18710,13 @@
       </c>
       <c r="H296" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I296" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I296" s="11" t="n"/>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18761,15 +18756,13 @@
       </c>
       <c r="H297" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I297" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I297" s="11" t="n"/>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -18815,7 +18808,7 @@
       <c r="I298" s="11" t="n"/>
       <c r="J298" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18861,7 +18854,7 @@
       <c r="I299" s="11" t="n"/>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18907,7 +18900,7 @@
       <c r="I300" s="11" t="n"/>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18946,7 @@
       <c r="I301" s="11" t="n"/>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18992,7 @@
       <c r="I302" s="11" t="n"/>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19038,7 @@
       <c r="I303" s="11" t="n"/>
       <c r="J303" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19084,7 @@
       <c r="I304" s="11" t="n"/>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19130,7 @@
       <c r="I305" s="11" t="n"/>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19176,7 @@
       <c r="I306" s="11" t="n"/>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19222,7 @@
       <c r="I307" s="11" t="n"/>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19275,7 +19268,7 @@
       <c r="I308" s="11" t="n"/>
       <c r="J308" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19314,7 @@
       <c r="I309" s="11" t="n"/>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19367,7 +19360,7 @@
       <c r="I310" s="11" t="n"/>
       <c r="J310" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19406,7 @@
       <c r="I311" s="11" t="n"/>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19453,15 +19446,13 @@
       </c>
       <c r="H312" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I312" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I312" s="11" t="n"/>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. probar_hu_bryan.py: POST /evidencias con uuid, lat/long y captura; reintento no duplica; queda antivirus PENDIENTE.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. probar_hu_bryan.py: POST /evidencias con uuid, lat/long y captura; reintento no duplica; queda antivirus PENDIENTE.</t>
         </is>
       </c>
     </row>
@@ -19501,15 +19492,13 @@
       </c>
       <c r="H313" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I313" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I313" s="11" t="n"/>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. MD actualizado.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD actualizado.</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19544,7 @@
       <c r="I314" s="11" t="n"/>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19590,7 @@
       <c r="I315" s="11" t="n"/>
       <c r="J315" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19636,7 @@
       <c r="I316" s="11" t="n"/>
       <c r="J316" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19682,7 @@
       <c r="I317" s="11" t="n"/>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19728,7 @@
       <c r="I318" s="11" t="n"/>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19774,7 @@
       <c r="I319" s="11" t="n"/>
       <c r="J319" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19820,7 @@
       <c r="I320" s="11" t="n"/>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19866,7 @@
       <c r="I321" s="11" t="n"/>
       <c r="J321" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19912,7 @@
       <c r="I322" s="11" t="n"/>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19958,7 @@
       <c r="I323" s="11" t="n"/>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20004,7 @@
       <c r="I324" s="11" t="n"/>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20050,7 @@
       <c r="I325" s="11" t="n"/>
       <c r="J325" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20096,7 @@
       <c r="I326" s="11" t="n"/>
       <c r="J326" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20142,7 @@
       <c r="I327" s="11" t="n"/>
       <c r="J327" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20188,7 @@
       <c r="I328" s="11" t="n"/>
       <c r="J328" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20234,7 @@
       <c r="I329" s="11" t="n"/>
       <c r="J329" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20280,7 @@
       <c r="I330" s="11" t="n"/>
       <c r="J330" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20326,7 @@
       <c r="I331" s="11" t="n"/>
       <c r="J331" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20372,7 @@
       <c r="I332" s="11" t="n"/>
       <c r="J332" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20418,7 @@
       <c r="I333" s="11" t="n"/>
       <c r="J333" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20464,7 @@
       <c r="I334" s="11" t="n"/>
       <c r="J334" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20510,7 @@
       <c r="I335" s="11" t="n"/>
       <c r="J335" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20556,7 @@
       <c r="I336" s="11" t="n"/>
       <c r="J336" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20602,7 @@
       <c r="I337" s="11" t="n"/>
       <c r="J337" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20648,7 @@
       <c r="I338" s="11" t="n"/>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20694,7 @@
       <c r="I339" s="11" t="n"/>
       <c r="J339" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20740,7 @@
       <c r="I340" s="11" t="n"/>
       <c r="J340" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20786,7 @@
       <c r="I341" s="11" t="n"/>
       <c r="J341" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20832,7 @@
       <c r="I342" s="11" t="n"/>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20878,7 @@
       <c r="I343" s="11" t="n"/>
       <c r="J343" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20924,7 @@
       <c r="I344" s="11" t="n"/>
       <c r="J344" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20970,7 @@
       <c r="I345" s="11" t="n"/>
       <c r="J345" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21016,7 @@
       <c r="I346" s="11" t="n"/>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21062,7 @@
       <c r="I347" s="11" t="n"/>
       <c r="J347" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21108,7 @@
       <c r="I348" s="11" t="n"/>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21154,7 @@
       <c r="I349" s="11" t="n"/>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21200,7 @@
       <c r="I350" s="11" t="n"/>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21246,7 @@
       <c r="I351" s="11" t="n"/>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21292,7 @@
       <c r="I352" s="11" t="n"/>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -21343,15 +21332,13 @@
       </c>
       <c r="H353" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I353" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I353" s="11" t="n"/>
       <c r="J353" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. probar_hu_bryan.py: finalizar registra duración y ejecutor; reintento con el mismo uuid -&gt; YA_ESTABA.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. probar_hu_bryan.py: finalizar registra duración y ejecutor; reintento con el mismo uuid -&gt; YA_ESTABA.</t>
         </is>
       </c>
     </row>
@@ -21391,15 +21378,13 @@
       </c>
       <c r="H354" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I354" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I354" s="11" t="n"/>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. MD 10.7.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.7.</t>
         </is>
       </c>
     </row>
@@ -21439,15 +21424,13 @@
       </c>
       <c r="H355" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I355" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I355" s="11" t="n"/>
       <c r="J355" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 4 como MVP de la app; se formaliza en el Sprint 6. La app ya consume el hilo en Mis tareas (sesiones anteriores).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. La app ya consume el hilo en Mis tareas (sesiones anteriores).</t>
         </is>
       </c>
     </row>
@@ -21487,15 +21470,13 @@
       </c>
       <c r="H356" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I356" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I356" s="11" t="n"/>
       <c r="J356" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Ya existía (nueva_orden_screen, encolada con uuid). Hoy además la correctiva nace desde la ficha de la falla (POST /fallas/{id}/orden).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía (nueva_orden_screen, encolada con uuid). Hoy además la correctiva nace desde la ficha de la falla (POST /fallas/{id}/orden).</t>
         </is>
       </c>
     </row>
@@ -21535,15 +21516,13 @@
       </c>
       <c r="H357" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I357" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I357" s="11" t="n"/>
       <c r="J357" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Orden_Trabajo_Paso: otp_obligatorio, otp_resultado_paso (4 PENDIENTE), otp_uuid con UQ_OTP_UUID (BD/209).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Orden_Trabajo_Paso: otp_obligatorio, otp_resultado_paso (4 PENDIENTE), otp_uuid con UQ_OTP_UUID (BD/209).</t>
         </is>
       </c>
     </row>
@@ -21583,15 +21562,13 @@
       </c>
       <c r="H358" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I358" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I358" s="11" t="n"/>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Los pasos viajan dentro de GET /ordenes-trabajo/{id} (API_SEL_ORDEN_TRABAJO_PASO), acotados al cliente y las plantas del usuario.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Los pasos viajan dentro de GET /ordenes-trabajo/{id} (API_SEL_ORDEN_TRABAJO_PASO), acotados al cliente y las plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -21631,15 +21608,13 @@
       </c>
       <c r="H359" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I359" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I359" s="11" t="n"/>
       <c r="J359" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. API_INS_ORDEN_TRABAJO_PASO idempotente por uuid (BD/209); el resultado de un paso por API_UPD_ORDEN_TRABAJO_PASO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_INS_ORDEN_TRABAJO_PASO idempotente por uuid (BD/209); el resultado de un paso por API_UPD_ORDEN_TRABAJO_PASO.</t>
         </is>
       </c>
     </row>
@@ -21679,15 +21654,13 @@
       </c>
       <c r="H360" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I360" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I360" s="11" t="n"/>
       <c r="J360" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OT-27..32 creadas desde la app con dos pasos obligatorios cada una.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OT-27..32 creadas desde la app con dos pasos obligatorios cada una.</t>
         </is>
       </c>
     </row>
@@ -21727,15 +21700,13 @@
       </c>
       <c r="H361" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I361" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I361" s="11" t="n"/>
       <c r="J361" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Sin endpoint /sync aparte: la ficha completa baja en un viaje y la sábana (bloque ORDENES_TRABAJO) cubre el offline.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Sin endpoint /sync aparte: la ficha completa baja en un viaje y la sábana (bloque ORDENES_TRABAJO) cubre el offline.</t>
         </is>
       </c>
     </row>
@@ -21775,15 +21746,13 @@
       </c>
       <c r="H362" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I362" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I362" s="11" t="n"/>
       <c r="J362" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. POST /ordenes-trabajo/pasos/{id} y POST /ordenes-trabajo/{id}/pasos, idempotentes por uuid, salen de la cola (outbox) uno a uno.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /ordenes-trabajo/pasos/{id} y POST /ordenes-trabajo/{id}/pasos, idempotentes por uuid, salen de la cola (outbox) uno a uno.</t>
         </is>
       </c>
     </row>
@@ -21823,15 +21792,13 @@
       </c>
       <c r="H363" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I363" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I363" s="11" t="n"/>
       <c r="J363" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Ya existía: FNC_SUSCRIPCION_VIGENTE → 402 en ApiBase.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Ya existía: FNC_SUSCRIPCION_VIGENTE → 402 en ApiBase.</t>
         </is>
       </c>
     </row>
@@ -21871,15 +21838,13 @@
       </c>
       <c r="H364" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I364" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I364" s="11" t="n"/>
       <c r="J364" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. orden_ficha_screen + hoja_paso: pestaña Pasos con objetivos grandes, conforme / no conforme / no aplica con comentario.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. orden_ficha_screen + hoja_paso: pestaña Pasos con objetivos grandes, conforme / no conforme / no aplica con comentario.</t>
         </is>
       </c>
     </row>
@@ -21919,15 +21884,13 @@
       </c>
       <c r="H365" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I365" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I365" s="11" t="n"/>
       <c r="J365" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OutboxService: SQLite primero, uuid al encolar; PASO en la cola.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OutboxService: SQLite primero, uuid al encolar; PASO en la cola.</t>
         </is>
       </c>
     </row>
@@ -21967,15 +21930,13 @@
       </c>
       <c r="H366" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I366" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I366" s="11" t="n"/>
       <c r="J366" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Reintento con el mismo uuid → misma respuesta (probado: reintento del alta devuelve el mismo id).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Reintento con el mismo uuid → misma respuesta (probado: reintento del alta devuelve el mismo id).</t>
         </is>
       </c>
     </row>
@@ -22015,15 +21976,13 @@
       </c>
       <c r="H367" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I367" s="11" t="n">
-        <v>1.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I367" s="11" t="n"/>
       <c r="J367" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. EJECUTAR ORDEN TRABAJO en el endpoint; el SP exige estar asignado y la OT en ejecución.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. EJECUTAR ORDEN TRABAJO en el endpoint; el SP exige estar asignado y la OT en ejecución.</t>
         </is>
       </c>
     </row>
@@ -22063,15 +22022,13 @@
       </c>
       <c r="H368" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I368" s="11" t="n">
-        <v>1.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I368" s="11" t="n"/>
       <c r="J368" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 conforme con ejecutor y hora · #2 no aplica con comentario · #3 obligatorio pendiente: ahora lo rechaza el SP y nombra los pasos (BD/227) · #4 medición: queda en la serie del activo vía /captura/mediciones (HU-043) · #5 offline: cola verificada en sesiones anteriores.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 conforme con ejecutor y hora · #2 no aplica con comentario · #3 obligatorio pendiente: ahora lo rechaza el SP y nombra los pasos (BD/227) · #4 medición: queda en la serie del activo vía /captura/mediciones (HU-043) · #5 offline: cola verificada en sesiones anteriores.</t>
         </is>
       </c>
     </row>
@@ -22111,15 +22068,13 @@
       </c>
       <c r="H369" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I369" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I369" s="11" t="n"/>
       <c r="J369" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. XML en OrdenesTrabajoController; MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. XML en OrdenesTrabajoController; MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -22159,15 +22114,13 @@
       </c>
       <c r="H370" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I370" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I370" s="11" t="n"/>
       <c r="J370" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Pendiente de la PO; historia En revisión.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Pendiente de la PO; historia En revisión.</t>
         </is>
       </c>
     </row>
@@ -22213,7 +22166,7 @@
       <c r="I371" s="11" t="n"/>
       <c r="J371" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22212,7 @@
       <c r="I372" s="11" t="n"/>
       <c r="J372" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22258,7 @@
       <c r="I373" s="11" t="n"/>
       <c r="J373" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22304,7 @@
       <c r="I374" s="11" t="n"/>
       <c r="J374" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22350,7 @@
       <c r="I375" s="11" t="n"/>
       <c r="J375" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22396,7 @@
       <c r="I376" s="11" t="n"/>
       <c r="J376" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22489,7 +22442,7 @@
       <c r="I377" s="11" t="n"/>
       <c r="J377" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22488,7 @@
       <c r="I378" s="11" t="n"/>
       <c r="J378" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22581,7 +22534,7 @@
       <c r="I379" s="11" t="n"/>
       <c r="J379" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22580,7 @@
       <c r="I380" s="11" t="n"/>
       <c r="J380" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22626,7 @@
       <c r="I381" s="11" t="n"/>
       <c r="J381" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22672,7 @@
       <c r="I382" s="11" t="n"/>
       <c r="J382" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22765,7 +22718,7 @@
       <c r="I383" s="11" t="n"/>
       <c r="J383" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22811,7 +22764,7 @@
       <c r="I384" s="11" t="n"/>
       <c r="J384" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -22851,15 +22804,13 @@
       </c>
       <c r="H385" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I385" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I385" s="11" t="n"/>
       <c r="J385" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Índices por cliente+estado existentes.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Índices por cliente+estado existentes.</t>
         </is>
       </c>
     </row>
@@ -22899,15 +22850,13 @@
       </c>
       <c r="H386" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I386" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I386" s="11" t="n"/>
       <c r="J386" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. API_SEL_ORDEN_TRABAJO_BANDEJA con @AMBITO 1/2/3, SITUACION (VENCIDA / VENCE HOY / EN PLAZO) calculada en el SP.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_SEL_ORDEN_TRABAJO_BANDEJA con @AMBITO 1/2/3, SITUACION (VENCIDA / VENCE HOY / EN PLAZO) calculada en el SP.</t>
         </is>
       </c>
     </row>
@@ -22947,15 +22896,13 @@
       </c>
       <c r="H387" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I387" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I387" s="11" t="n"/>
       <c r="J387" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Cubierto por los índices existentes.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Cubierto por los índices existentes.</t>
         </is>
       </c>
     </row>
@@ -22995,15 +22942,13 @@
       </c>
       <c r="H388" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I388" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I388" s="11" t="n"/>
       <c r="J388" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OT-27..32 de prueba; bandeja de Cristián con 5 y disponibles 10.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OT-27..32 de prueba; bandeja de Cristián con 5 y disponibles 10.</t>
         </is>
       </c>
     </row>
@@ -23043,15 +22988,13 @@
       </c>
       <c r="H389" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I389" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I389" s="11" t="n"/>
       <c r="J389" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. GET /ordenes-trabajo?ambito=&amp;instalacion=&amp;desde= (paginado en el SP).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /ordenes-trabajo?ambito=&amp;instalacion=&amp;desde= (paginado en el SP).</t>
         </is>
       </c>
     </row>
@@ -23091,15 +23034,13 @@
       </c>
       <c r="H390" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I390" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I390" s="11" t="n"/>
       <c r="J390" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. No hay caché en servidor: la app guarda la última bandeja en SQLite (sábana) y la muestra sin señal, que es lo que pide el criterio 2.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. No hay caché en servidor: la app guarda la última bandeja en SQLite (sábana) y la muestra sin señal, que es lo que pide el criterio 2.</t>
         </is>
       </c>
     </row>
@@ -23139,15 +23080,13 @@
       </c>
       <c r="H391" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I391" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I391" s="11" t="n"/>
       <c r="J391" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. ordenes_screen.dart: pestañas Mías / Disponibles / Planta; mi_trabajo_screen une órdenes, tareas y pautas.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. ordenes_screen.dart: pestañas Mías / Disponibles / Planta; mi_trabajo_screen une órdenes, tareas y pautas.</t>
         </is>
       </c>
     </row>
@@ -23187,15 +23126,13 @@
       </c>
       <c r="H392" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I392" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I392" s="11" t="n"/>
       <c r="J392" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. VER ORDENES TRABAJO; el SP filtra por cliente y plantas del usuario.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. VER ORDENES TRABAJO; el SP filtra por cliente y plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -23235,15 +23172,13 @@
       </c>
       <c r="H393" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I393" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I393" s="11" t="n"/>
       <c r="J393" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 bandeja con SITUACION (HTTP) · #2 sin conexión desde la sábana (verificado en sesiones anteriores, bloque ORDENES_TRABAJO) · #3 disponibles: la OT nueva aparece sin dueño (HTTP).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 bandeja con SITUACION (HTTP) · #2 sin conexión desde la sábana (verificado en sesiones anteriores, bloque ORDENES_TRABAJO) · #3 disponibles: la OT nueva aparece sin dueño (HTTP).</t>
         </is>
       </c>
     </row>
@@ -23283,15 +23218,13 @@
       </c>
       <c r="H394" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I394" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I394" s="11" t="n"/>
       <c r="J394" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -23331,15 +23264,13 @@
       </c>
       <c r="H395" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I395" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I395" s="11" t="n"/>
       <c r="J395" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. hoja_asignar.dart: responsable o apoyo desde la ficha de la OT, con la gente de la planta; encolada con uuid (BD/226).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. hoja_asignar.dart: responsable o apoyo desde la ficha de la OT, con la gente de la planta; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -23379,15 +23310,13 @@
       </c>
       <c r="H396" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I396" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I396" s="11" t="n"/>
       <c r="J396" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Orden_Trabajo_Asignacion con UX_OTA_RESPONSABLE filtrado.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Orden_Trabajo_Asignacion con UX_OTA_RESPONSABLE filtrado.</t>
         </is>
       </c>
     </row>
@@ -23427,15 +23356,13 @@
       </c>
       <c r="H397" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I397" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I397" s="11" t="n"/>
       <c r="J397" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. API_UPD_ORDEN_TRABAJO_TOMAR: UPDATE … WHERE estado = 1 con @@ROWCOUNT (la carrera se resuelve en la base).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_UPD_ORDEN_TRABAJO_TOMAR: UPDATE … WHERE estado = 1 con @@ROWCOUNT (la carrera se resuelve en la base).</t>
         </is>
       </c>
     </row>
@@ -23475,15 +23402,13 @@
       </c>
       <c r="H398" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I398" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I398" s="11" t="n"/>
       <c r="J398" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. La regla vive en el SP; web y app reciben el mismo veredicto.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. La regla vive en el SP; web y app reciben el mismo veredicto.</t>
         </is>
       </c>
     </row>
@@ -23523,15 +23448,13 @@
       </c>
       <c r="H399" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I399" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I399" s="11" t="n"/>
       <c r="J399" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. El resultado se lee en GET /ordenes-trabajo/{id} (estado y asignados).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. El resultado se lee en GET /ordenes-trabajo/{id} (estado y asignados).</t>
         </is>
       </c>
     </row>
@@ -23571,15 +23494,13 @@
       </c>
       <c r="H400" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I400" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I400" s="11" t="n"/>
       <c r="J400" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OT-29: Cristián toma, Paula llega segunda.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OT-29: Cristián toma, Paula llega segunda.</t>
         </is>
       </c>
     </row>
@@ -23619,15 +23540,13 @@
       </c>
       <c r="H401" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I401" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I401" s="11" t="n"/>
       <c r="J401" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. POST /ordenes-trabajo/{id}/tomar.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /ordenes-trabajo/{id}/tomar.</t>
         </is>
       </c>
     </row>
@@ -23667,15 +23586,13 @@
       </c>
       <c r="H402" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I402" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I402" s="11" t="n"/>
       <c r="J402" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. «La orden ya fue tomada por otro usuario o no está abierta» llega como 400 de negocio con mensaje, no como 500.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. «La orden ya fue tomada por otro usuario o no está abierta» llega como 400 de negocio con mensaje, no como 500.</t>
         </is>
       </c>
     </row>
@@ -23715,15 +23632,13 @@
       </c>
       <c r="H403" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I403" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I403" s="11" t="n"/>
       <c r="J403" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Botón «Tomar trabajo» en la ficha; arranca el cronómetro.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Botón «Tomar trabajo» en la ficha; arranca el cronómetro.</t>
         </is>
       </c>
     </row>
@@ -23763,15 +23678,13 @@
       </c>
       <c r="H404" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I404" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I404" s="11" t="n"/>
       <c r="J404" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. TOMAR ORDEN TRABAJO en el endpoint.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. TOMAR ORDEN TRABAJO en el endpoint.</t>
         </is>
       </c>
     </row>
@@ -23811,15 +23724,13 @@
       </c>
       <c r="H405" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I405" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I405" s="11" t="n"/>
       <c r="J405" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 toma → EN EJECUCION y responsable · #2 dos técnicos: el segundo recibe «ya fue tomada» · #3 sumar compañero: dos asignados, un responsable (POST asignaciones con es_responsable=false).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 toma → EN EJECUCION y responsable · #2 dos técnicos: el segundo recibe «ya fue tomada» · #3 sumar compañero: dos asignados, un responsable (POST asignaciones con es_responsable=false).</t>
         </is>
       </c>
     </row>
@@ -23859,15 +23770,13 @@
       </c>
       <c r="H406" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I406" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I406" s="11" t="n"/>
       <c r="J406" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -23907,15 +23816,13 @@
       </c>
       <c r="H407" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I407" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I407" s="11" t="n"/>
       <c r="J407" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Orden_Trabajo_Repuesto: consumida / devuelta / costo unitario; uuid del movimiento.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Orden_Trabajo_Repuesto: consumida / devuelta / costo unitario; uuid del movimiento.</t>
         </is>
       </c>
     </row>
@@ -23955,15 +23862,13 @@
       </c>
       <c r="H408" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I408" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I408" s="11" t="n"/>
       <c r="J408" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. API_INS_ORDEN_TRABAJO_REPUESTO mueve inventario y orden en una transacción; exige ubicación si la bodega las tiene.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_INS_ORDEN_TRABAJO_REPUESTO mueve inventario y orden en una transacción; exige ubicación si la bodega las tiene.</t>
         </is>
       </c>
     </row>
@@ -24003,15 +23908,13 @@
       </c>
       <c r="H409" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I409" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I409" s="11" t="n"/>
       <c r="J409" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. GET /ordenes-trabajo/{id}/recursos (repuestos con consumido y devuelto) y /repuestos-disponibles con ES_COMPATIBLE.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /ordenes-trabajo/{id}/recursos (repuestos con consumido y devuelto) y /repuestos-disponibles con ES_COMPATIBLE.</t>
         </is>
       </c>
     </row>
@@ -24051,15 +23954,13 @@
       </c>
       <c r="H410" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I410" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I410" s="11" t="n"/>
       <c r="J410" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. No hay UPD: consumo y devolución son movimientos (append), la corrección es una devolución.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. No hay UPD: consumo y devolución son movimientos (append), la corrección es una devolución.</t>
         </is>
       </c>
     </row>
@@ -24099,15 +24000,13 @@
       </c>
       <c r="H411" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I411" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I411" s="11" t="n"/>
       <c r="J411" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. REP-6205 en Bodega Frío: consumido 1 y devuelto 1 sobre OT-31.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. REP-6205 en Bodega Frío: consumido 1 y devuelto 1 sobre OT-31.</t>
         </is>
       </c>
     </row>
@@ -24147,15 +24046,13 @@
       </c>
       <c r="H412" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I412" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I412" s="11" t="n"/>
       <c r="J412" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. POST /ordenes-trabajo/{id}/repuestos idempotente por uuid (reintento no consume dos veces).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /ordenes-trabajo/{id}/repuestos idempotente por uuid (reintento no consume dos veces).</t>
         </is>
       </c>
     </row>
@@ -24195,15 +24092,13 @@
       </c>
       <c r="H413" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I413" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I413" s="11" t="n"/>
       <c r="J413" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Cubierto por /recursos y /repuestos-disponibles.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Cubierto por /recursos y /repuestos-disponibles.</t>
         </is>
       </c>
     </row>
@@ -24243,15 +24138,13 @@
       </c>
       <c r="H414" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I414" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I414" s="11" t="n"/>
       <c r="J414" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OrdenTrabajoRepuestoAltaDto; ExigirCuerpo.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OrdenTrabajoRepuestoAltaDto; ExigirCuerpo.</t>
         </is>
       </c>
     </row>
@@ -24291,15 +24184,13 @@
       </c>
       <c r="H415" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I415" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I415" s="11" t="n"/>
       <c r="J415" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. hojas_recursos.dart: consumo y devolución con bodega y estante. Defecto corregido hoy: GET /bodegas/{id}/ubicaciones daba 403 al técnico (VER BODEGAS) y dejaba el consumo sin camino; ahora acepta EJECUTAR ORDEN TRABAJO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. hojas_recursos.dart: consumo y devolución con bodega y estante. Defecto corregido hoy: GET /bodegas/{id}/ubicaciones daba 403 al técnico (VER BODEGAS) y dejaba el consumo sin camino; ahora acepta EJECUTAR ORDEN TRABAJO.</t>
         </is>
       </c>
     </row>
@@ -24339,15 +24230,13 @@
       </c>
       <c r="H416" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I416" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I416" s="11" t="n"/>
       <c r="J416" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. EJECUTAR ORDEN TRABAJO; cliente del token.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. EJECUTAR ORDEN TRABAJO; cliente del token.</t>
         </is>
       </c>
     </row>
@@ -24387,15 +24276,13 @@
       </c>
       <c r="H417" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I417" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I417" s="11" t="n"/>
       <c r="J417" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 consumo descuenta y suma costo (SP en transacción) · #2 horómetro de la pieza: campos opcionales del DTO (no verificado con datos) · #3 devolución: consumido 0, devuelto 1.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 consumo descuenta y suma costo (SP en transacción) · #2 horómetro de la pieza: campos opcionales del DTO (no verificado con datos) · #3 devolución: consumido 0, devuelto 1.</t>
         </is>
       </c>
     </row>
@@ -24435,15 +24322,13 @@
       </c>
       <c r="H418" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I418" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I418" s="11" t="n"/>
       <c r="J418" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -24483,15 +24368,13 @@
       </c>
       <c r="H419" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I419" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I419" s="11" t="n"/>
       <c r="J419" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. otr_resultado, otr_fecha_fin_real_utc, otr_duracion_real_minuto.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. otr_resultado, otr_fecha_fin_real_utc, otr_duracion_real_minuto.</t>
         </is>
       </c>
     </row>
@@ -24531,15 +24414,13 @@
       </c>
       <c r="H420" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I420" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I420" s="11" t="n"/>
       <c r="J420" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. BD/227 UPD_ORDEN_TRABAJO_FINALIZAR: rechaza con los nombres de los obligatorios pendientes, guarda resultado y fecha fin real, advierte sin mano de obra.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. BD/227 UPD_ORDEN_TRABAJO_FINALIZAR: rechaza con los nombres de los obligatorios pendientes, guarda resultado y fecha fin real, advierte sin mano de obra.</t>
         </is>
       </c>
     </row>
@@ -24579,15 +24460,13 @@
       </c>
       <c r="H421" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I421" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I421" s="11" t="n"/>
       <c r="J421" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. La regla pasó del botón de la app al SP: probado por HTTP que antes el endpoint dejaba finalizar con obligatorios pendientes.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. La regla pasó del botón de la app al SP: probado por HTTP que antes el endpoint dejaba finalizar con obligatorios pendientes.</t>
         </is>
       </c>
     </row>
@@ -24627,15 +24506,13 @@
       </c>
       <c r="H422" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I422" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I422" s="11" t="n"/>
       <c r="J422" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. El SP devuelve ORDEN_TRABAJO, ESTADO, ADVERTENCIA; la API la expone como `advertencia`.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. El SP devuelve ORDEN_TRABAJO, ESTADO, ADVERTENCIA; la API la expone como `advertencia`.</t>
         </is>
       </c>
     </row>
@@ -24675,15 +24552,13 @@
       </c>
       <c r="H423" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I423" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I423" s="11" t="n"/>
       <c r="J423" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. OT-29..32.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. OT-29..32.</t>
         </is>
       </c>
     </row>
@@ -24723,15 +24598,13 @@
       </c>
       <c r="H424" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I424" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I424" s="11" t="n"/>
       <c r="J424" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. POST /ordenes-trabajo/{id}/finalizar → 200 {otr_id, advertencia}.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /ordenes-trabajo/{id}/finalizar → 200 {otr_id, advertencia}.</t>
         </is>
       </c>
     </row>
@@ -24771,15 +24644,13 @@
       </c>
       <c r="H425" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I425" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I425" s="11" t="n"/>
       <c r="J425" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. «Faltan pasos obligatorios por resolver: Revisar rodamiento, Medir vibración» → 400 con mensaje.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. «Faltan pasos obligatorios por resolver: Revisar rodamiento, Medir vibración» → 400 con mensaje.</t>
         </is>
       </c>
     </row>
@@ -24819,15 +24690,13 @@
       </c>
       <c r="H426" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I426" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I426" s="11" t="n"/>
       <c r="J426" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. orden_ficha_screen: diálogo de resultado, tiempo del cronómetro como mano de obra, y la advertencia del servidor en pantalla.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. orden_ficha_screen: diálogo de resultado, tiempo del cronómetro como mano de obra, y la advertencia del servidor en pantalla.</t>
         </is>
       </c>
     </row>
@@ -24867,15 +24736,13 @@
       </c>
       <c r="H427" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I427" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I427" s="11" t="n"/>
       <c r="J427" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. EJECUTAR ORDEN TRABAJO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. EJECUTAR ORDEN TRABAJO.</t>
         </is>
       </c>
     </row>
@@ -24915,15 +24782,13 @@
       </c>
       <c r="H428" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I428" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I428" s="11" t="n"/>
       <c r="J428" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 finaliza → EN ESPERA DE CIERRE y no se modifica (paso rechazado) · #2 obligatorios pendientes → 400 con nombres · #3 sin mano de obra → advertencia y se permite (SP).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 finaliza → EN ESPERA DE CIERRE y no se modifica (paso rechazado) · #2 obligatorios pendientes → 400 con nombres · #3 sin mano de obra → advertencia y se permite (SP).</t>
         </is>
       </c>
     </row>
@@ -24963,15 +24828,13 @@
       </c>
       <c r="H429" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I429" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I429" s="11" t="n"/>
       <c r="J429" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -25011,15 +24874,13 @@
       </c>
       <c r="H430" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I430" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I430" s="11" t="n"/>
       <c r="J430" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Orden_Trabajo_Mano_Obra: usuario o proveedor, minutos, costo hora y moneda, uuid.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Orden_Trabajo_Mano_Obra: usuario o proveedor, minutos, costo hora y moneda, uuid.</t>
         </is>
       </c>
     </row>
@@ -25059,15 +24920,13 @@
       </c>
       <c r="H431" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I431" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I431" s="11" t="n"/>
       <c r="J431" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. API_INS_ORDEN_TRABAJO_MANO_OBRA (BD/193) + BD/227: el ejecutante se valida antes de insertar.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. API_INS_ORDEN_TRABAJO_MANO_OBRA (BD/193) + BD/227: el ejecutante se valida antes de insertar.</t>
         </is>
       </c>
     </row>
@@ -25107,15 +24966,13 @@
       </c>
       <c r="H432" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I432" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I432" s="11" t="n"/>
       <c r="J432" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. GET /ordenes-trabajo/{id}/recursos.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. GET /ordenes-trabajo/{id}/recursos.</t>
         </is>
       </c>
     </row>
@@ -25155,15 +25012,13 @@
       </c>
       <c r="H433" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I433" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I433" s="11" t="n"/>
       <c r="J433" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Append-only: no hay UPD, se corrige agregando otro tramo.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Append-only: no hay UPD, se corrige agregando otro tramo.</t>
         </is>
       </c>
     </row>
@@ -25203,15 +25058,13 @@
       </c>
       <c r="H434" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I434" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I434" s="11" t="n"/>
       <c r="J434" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Tramo de 90 min sobre OT-29..32.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Tramo de 90 min sobre OT-29..32.</t>
         </is>
       </c>
     </row>
@@ -25251,15 +25104,13 @@
       </c>
       <c r="H435" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I435" s="11" t="n">
-        <v>0.75</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I435" s="11" t="n"/>
       <c r="J435" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. POST /ordenes-trabajo/{id}/mano-obra idempotente por uuid.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. POST /ordenes-trabajo/{id}/mano-obra idempotente por uuid.</t>
         </is>
       </c>
     </row>
@@ -25299,15 +25150,13 @@
       </c>
       <c r="H436" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I436" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I436" s="11" t="n"/>
       <c r="J436" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. Cubierto por /recursos.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. Cubierto por /recursos.</t>
         </is>
       </c>
     </row>
@@ -25347,15 +25196,13 @@
       </c>
       <c r="H437" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I437" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I437" s="11" t="n"/>
       <c r="J437" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. ManoObraAltaDto.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. ManoObraAltaDto.</t>
         </is>
       </c>
     </row>
@@ -25395,15 +25242,13 @@
       </c>
       <c r="H438" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I438" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I438" s="11" t="n"/>
       <c r="J438" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. hojas_recursos.dart (tramo manual) y cronómetro que se anota al finalizar.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. hojas_recursos.dart (tramo manual) y cronómetro que se anota al finalizar.</t>
         </is>
       </c>
     </row>
@@ -25443,15 +25288,13 @@
       </c>
       <c r="H439" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I439" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I439" s="11" t="n"/>
       <c r="J439" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. EJECUTAR ORDEN TRABAJO; plantas del usuario.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. EJECUTAR ORDEN TRABAJO; plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -25491,15 +25334,13 @@
       </c>
       <c r="H440" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I440" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I440" s="11" t="n"/>
       <c r="J440" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. #1 minutos calculados = 90 y duración real = suma · #2 externa: proveedor y valor hora en el modelo (no verificado con datos de proveedor) · #3 sin ejecutante válido → rechazado con mensaje (antes FK cruda).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. #1 minutos calculados = 90 y duración real = suma · #2 externa: proveedor y valor hora en el modelo (no verificado con datos de proveedor) · #3 sin ejecutante válido → rechazado con mensaje (antes FK cruda).</t>
         </is>
       </c>
     </row>
@@ -25539,15 +25380,13 @@
       </c>
       <c r="H441" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I441" s="11" t="n">
-        <v>0.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I441" s="11" t="n"/>
       <c r="J441" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. MD 10.11.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -25587,15 +25426,13 @@
       </c>
       <c r="H442" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I442" s="11" t="n">
-        <v>1.25</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I442" s="11" t="n"/>
       <c r="J442" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. fallas_screen / nueva_falla_screen / falla_ficha_screen: registrar, diagnósticos, acciones, parada y abrir la correctiva; menú app://fallas; todo encolado con uuid (BD/226).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. fallas_screen / nueva_falla_screen / falla_ficha_screen: registrar, diagnósticos, acciones, parada y abrir la correctiva; menú app://fallas; todo encolado con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -25635,15 +25472,13 @@
       </c>
       <c r="H443" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I443" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I443" s="11" t="n"/>
       <c r="J443" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. hoja_indisponibilidad.dart desde la OT y desde la falla; encolada con uuid (BD/226).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. hoja_indisponibilidad.dart desde la OT y desde la falla; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25524,7 @@
       <c r="I444" s="11" t="n"/>
       <c r="J444" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25735,7 +25570,7 @@
       <c r="I445" s="11" t="n"/>
       <c r="J445" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25616,7 @@
       <c r="I446" s="11" t="n"/>
       <c r="J446" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25827,7 +25662,7 @@
       <c r="I447" s="11" t="n"/>
       <c r="J447" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25873,7 +25708,7 @@
       <c r="I448" s="11" t="n"/>
       <c r="J448" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25919,7 +25754,7 @@
       <c r="I449" s="11" t="n"/>
       <c r="J449" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -25965,7 +25800,7 @@
       <c r="I450" s="11" t="n"/>
       <c r="J450" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26011,7 +25846,7 @@
       <c r="I451" s="11" t="n"/>
       <c r="J451" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26057,7 +25892,7 @@
       <c r="I452" s="11" t="n"/>
       <c r="J452" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26103,7 +25938,7 @@
       <c r="I453" s="11" t="n"/>
       <c r="J453" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26149,7 +25984,7 @@
       <c r="I454" s="11" t="n"/>
       <c r="J454" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26195,7 +26030,7 @@
       <c r="I455" s="11" t="n"/>
       <c r="J455" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26241,7 +26076,7 @@
       <c r="I456" s="11" t="n"/>
       <c r="J456" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26287,7 +26122,7 @@
       <c r="I457" s="11" t="n"/>
       <c r="J457" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26333,7 +26168,7 @@
       <c r="I458" s="11" t="n"/>
       <c r="J458" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26214,7 @@
       <c r="I459" s="11" t="n"/>
       <c r="J459" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26425,7 +26260,7 @@
       <c r="I460" s="11" t="n"/>
       <c r="J460" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26471,7 +26306,7 @@
       <c r="I461" s="11" t="n"/>
       <c r="J461" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26517,7 +26352,7 @@
       <c r="I462" s="11" t="n"/>
       <c r="J462" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26398,7 @@
       <c r="I463" s="11" t="n"/>
       <c r="J463" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26444,7 @@
       <c r="I464" s="11" t="n"/>
       <c r="J464" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26655,7 +26490,7 @@
       <c r="I465" s="11" t="n"/>
       <c r="J465" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26701,7 +26536,7 @@
       <c r="I466" s="11" t="n"/>
       <c r="J466" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26747,7 +26582,7 @@
       <c r="I467" s="11" t="n"/>
       <c r="J467" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26793,7 +26628,7 @@
       <c r="I468" s="11" t="n"/>
       <c r="J468" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26839,7 +26674,7 @@
       <c r="I469" s="11" t="n"/>
       <c r="J469" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26720,7 @@
       <c r="I470" s="11" t="n"/>
       <c r="J470" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26766,7 @@
       <c r="I471" s="11" t="n"/>
       <c r="J471" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -26977,7 +26812,7 @@
       <c r="I472" s="11" t="n"/>
       <c r="J472" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27023,7 +26858,7 @@
       <c r="I473" s="11" t="n"/>
       <c r="J473" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27069,7 +26904,7 @@
       <c r="I474" s="11" t="n"/>
       <c r="J474" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27115,7 +26950,7 @@
       <c r="I475" s="11" t="n"/>
       <c r="J475" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27161,7 +26996,7 @@
       <c r="I476" s="11" t="n"/>
       <c r="J476" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27207,7 +27042,7 @@
       <c r="I477" s="11" t="n"/>
       <c r="J477" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27253,7 +27088,7 @@
       <c r="I478" s="11" t="n"/>
       <c r="J478" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27299,7 +27134,7 @@
       <c r="I479" s="11" t="n"/>
       <c r="J479" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27345,7 +27180,7 @@
       <c r="I480" s="11" t="n"/>
       <c r="J480" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27226,7 @@
       <c r="I481" s="11" t="n"/>
       <c r="J481" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27431,15 +27266,13 @@
       </c>
       <c r="H482" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I482" s="11" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I482" s="11" t="n"/>
       <c r="J482" s="12" t="inlineStr">
         <is>
-          <t>Adelantada durante el Sprint 5 como MVP de la app; se formaliza en el Sprint 6. hoja_firma.dart + BloqueFirmas en la ficha de la OT.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado. hoja_firma.dart + BloqueFirmas en la ficha de la OT.</t>
         </is>
       </c>
     </row>
@@ -27485,7 +27318,7 @@
       <c r="I483" s="11" t="n"/>
       <c r="J483" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27364,7 @@
       <c r="I484" s="11" t="n"/>
       <c r="J484" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27577,7 +27410,7 @@
       <c r="I485" s="11" t="n"/>
       <c r="J485" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27623,7 +27456,7 @@
       <c r="I486" s="11" t="n"/>
       <c r="J486" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27669,7 +27502,7 @@
       <c r="I487" s="11" t="n"/>
       <c r="J487" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27548,7 @@
       <c r="I488" s="11" t="n"/>
       <c r="J488" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27594,7 @@
       <c r="I489" s="11" t="n"/>
       <c r="J489" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27807,7 +27640,7 @@
       <c r="I490" s="11" t="n"/>
       <c r="J490" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27853,7 +27686,7 @@
       <c r="I491" s="11" t="n"/>
       <c r="J491" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27899,7 +27732,7 @@
       <c r="I492" s="11" t="n"/>
       <c r="J492" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27945,7 +27778,7 @@
       <c r="I493" s="11" t="n"/>
       <c r="J493" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -27991,7 +27824,7 @@
       <c r="I494" s="11" t="n"/>
       <c r="J494" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28037,7 +27870,7 @@
       <c r="I495" s="11" t="n"/>
       <c r="J495" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28083,7 +27916,7 @@
       <c r="I496" s="11" t="n"/>
       <c r="J496" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28129,7 +27962,7 @@
       <c r="I497" s="11" t="n"/>
       <c r="J497" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28175,7 +28008,7 @@
       <c r="I498" s="11" t="n"/>
       <c r="J498" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28221,7 +28054,7 @@
       <c r="I499" s="11" t="n"/>
       <c r="J499" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28267,7 +28100,7 @@
       <c r="I500" s="11" t="n"/>
       <c r="J500" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28146,7 @@
       <c r="I501" s="11" t="n"/>
       <c r="J501" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28359,7 +28192,7 @@
       <c r="I502" s="11" t="n"/>
       <c r="J502" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28405,7 +28238,7 @@
       <c r="I503" s="11" t="n"/>
       <c r="J503" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28284,7 @@
       <c r="I504" s="11" t="n"/>
       <c r="J504" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28330,7 @@
       <c r="I505" s="11" t="n"/>
       <c r="J505" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28376,7 @@
       <c r="I506" s="11" t="n"/>
       <c r="J506" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28422,7 @@
       <c r="I507" s="11" t="n"/>
       <c r="J507" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
@@ -28635,7 +28468,237 @@
       <c r="I508" s="11" t="n"/>
       <c r="J508" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="11" t="inlineStr">
+        <is>
+          <t>T-6301</t>
+        </is>
+      </c>
+      <c r="B509" s="11" t="inlineStr">
+        <is>
+          <t>HU-004</t>
+        </is>
+      </c>
+      <c r="C509" s="12" t="inlineStr">
+        <is>
+          <t>Recuperar mi contraseña</t>
+        </is>
+      </c>
+      <c r="D509" s="17" t="inlineStr">
+        <is>
+          <t>Infraestructura: configurar el servidor SMTP (host, puerto, usuario, clave) en Web.config y verificar el envío real del correo de recuperación. Impedimento n.º 1, reprogramado al Sprint 6 en la Sprint Review 1.</t>
+        </is>
+      </c>
+      <c r="E509" s="11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F509" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G509" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="H509" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I509" s="11" t="n"/>
+      <c r="J509" s="12" t="inlineStr">
+        <is>
+          <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="11" t="inlineStr">
+        <is>
+          <t>T-6302</t>
+        </is>
+      </c>
+      <c r="B510" s="11" t="inlineStr">
+        <is>
+          <t>HU-140</t>
+        </is>
+      </c>
+      <c r="C510" s="12" t="inlineStr">
+        <is>
+          <t>Adjuntar evidencias desde terreno</t>
+        </is>
+      </c>
+      <c r="D510" s="17" t="inlineStr">
+        <is>
+          <t>Infraestructura: decidir el proveedor y levantar la API de almacenamiento de archivos (AlmacenamientoApiUrl); probar carga, descarga y antivirus. Impedimento n.º 2.</t>
+        </is>
+      </c>
+      <c r="E510" s="11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F510" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G510" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H510" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I510" s="11" t="n"/>
+      <c r="J510" s="12" t="inlineStr">
+        <is>
+          <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="11" t="inlineStr">
+        <is>
+          <t>T-6303</t>
+        </is>
+      </c>
+      <c r="B511" s="11" t="inlineStr">
+        <is>
+          <t>HU-011</t>
+        </is>
+      </c>
+      <c r="C511" s="12" t="inlineStr">
+        <is>
+          <t>Administrar las plantas del cliente</t>
+        </is>
+      </c>
+      <c r="D511" s="17" t="inlineStr">
+        <is>
+          <t>Infraestructura: restringir la clave de Google Maps por referrer HTTP y APIs habilitadas en la consola de Google Cloud. Impedimento n.º 4.</t>
+        </is>
+      </c>
+      <c r="E511" s="11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F511" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G511" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H511" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I511" s="11" t="n"/>
+      <c r="J511" s="12" t="inlineStr">
+        <is>
+          <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="11" t="inlineStr">
+        <is>
+          <t>T-6304</t>
+        </is>
+      </c>
+      <c r="B512" s="11" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="C512" s="12" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="D512" s="17" t="inlineStr">
+        <is>
+          <t>Infraestructura: proyecto Firebase Cloud Messaging, credenciales del servidor y registro de dispositivos para las notificaciones push de la app.</t>
+        </is>
+      </c>
+      <c r="E512" s="11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F512" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G512" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="H512" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I512" s="11" t="n"/>
+      <c r="J512" s="12" t="inlineStr">
+        <is>
+          <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="11" t="inlineStr">
+        <is>
+          <t>T-6305</t>
+        </is>
+      </c>
+      <c r="B513" s="11" t="inlineStr">
+        <is>
+          <t>HU-001</t>
+        </is>
+      </c>
+      <c r="C513" s="12" t="inlineStr">
+        <is>
+          <t>Iniciar sesión en SIGMA</t>
+        </is>
+      </c>
+      <c r="D513" s="17" t="inlineStr">
+        <is>
+          <t>Infraestructura: publicar la API en el dominio definitivo con HTTPS (certificado, JWT_ISSUER/AUDIENCE) para que la app entre desde fuera de la red del equipo.</t>
+        </is>
+      </c>
+      <c r="E513" s="11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F513" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G513" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H513" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I513" s="11" t="n"/>
+      <c r="J513" s="12" t="inlineStr">
+        <is>
+          <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -6078,6 +6078,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -11752,11 +11754,17 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I139" s="11" t="n"/>
-      <c r="J139" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML: los tres modelos existen como semilla SQL (BD/245/247/248). Falta el INS_MODELO_PREDICTIVO del mantenedor.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="55.2" customHeight="1" s="19">
       <c r="A140" s="11" t="inlineStr">
@@ -12004,11 +12012,17 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I145" s="11" t="n"/>
-      <c r="J145" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML (BD/245): menú SIGMA AI › Experimentos registrado con permiso VER PREDICCIONES.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="27.6" customHeight="1" s="19">
       <c r="A146" s="11" t="inlineStr">
@@ -12218,7 +12232,11 @@
         </is>
       </c>
       <c r="I150" s="11" t="n"/>
-      <c r="J150" s="12" t="n"/>
+      <c r="J150" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por la investigación (mpv_parametro, mpv_registro, mpv_fecha_verificacion_utc; BD/245–246). Revisar en Sprint Planning 6.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="41.4" customHeight="1" s="19">
       <c r="A151" s="11" t="inlineStr">
@@ -12260,7 +12278,11 @@
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
-      <c r="J151" s="12" t="n"/>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por la investigación (API_INS_ML_ENTRENAMIENTO + API_INS_ML_MODELO_VERSION, Bryan). Revisar en Sprint Planning 6.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="55.2" customHeight="1" s="19">
       <c r="A152" s="11" t="inlineStr">
@@ -12298,11 +12320,17 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="n"/>
-      <c r="J152" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML (BD/245–246): reglas en API_INS_ML_MODELO_VERSION (pesos válidos), API_UPD_ML_MODELO_VERSION_PUBLICAR (retira la anterior), API_UPD_ML_MODELO_VERSION_ARTEFACTO (hash del ONNX de Azure).</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="41.4" customHeight="1" s="19">
       <c r="A153" s="11" t="inlineStr">
@@ -12344,7 +12372,11 @@
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
-      <c r="J153" s="12" t="n"/>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por la investigación (API_SEL_ML @TIPO 3 y 4). Revisar en Sprint Planning 6.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="41.4" customHeight="1" s="19">
       <c r="A154" s="11" t="inlineStr">
@@ -12386,7 +12418,11 @@
         </is>
       </c>
       <c r="I154" s="11" t="n"/>
-      <c r="J154" s="12" t="n"/>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>Datos reales: versiones v1–v2 (FAILURE), v1 (RUL), v1 (VISION) registradas en Azure ML; las sintéticas marcadas en la observación.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="27.6" customHeight="1" s="19">
       <c r="A155" s="11" t="inlineStr">
@@ -12428,7 +12464,11 @@
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
-      <c r="J155" s="12" t="n"/>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta parcialmente por SIGMA AI › Experimentos (tarjetas 2 y 3: corridas, versiones, publicar, verificar en Azure). Falta comparar versiones lado a lado (criterio 3).</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="41.4" customHeight="1" s="19">
       <c r="A156" s="11" t="inlineStr">
@@ -12466,11 +12506,17 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J156" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML: permiso ENTRENAR MODELOS en la API (ExigirPermiso) y función «Entrenar y publicar» en la web.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="41.4" customHeight="1" s="19">
       <c r="A157" s="11" t="inlineStr">
@@ -12634,11 +12680,17 @@
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="n"/>
-      <c r="J160" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML (BD/245–247): Dataset_Entrenamiento revisado; FNC_ML_ACTIVO_HISTORICO_V1 y FNC_ML_COMPONENTE_HISTORICO_V1 (sin fuga, con censura).</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="27.6" customHeight="1" s="19">
       <c r="A161" s="11" t="inlineStr">
@@ -12680,7 +12732,11 @@
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
-      <c r="J161" s="12" t="n"/>
+      <c r="J161" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por la investigación (API_SEL_ML_DATASET_FALLA/RUL/VISION + API_INS_ML_DATASET, Bryan). Revisar en Sprint Planning 6.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="27.6" customHeight="1" s="19">
       <c r="A162" s="11" t="inlineStr">
@@ -12722,7 +12778,11 @@
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
-      <c r="J162" s="12" t="n"/>
+      <c r="J162" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por la investigación (reglas en los SP de dataset, Bryan). Revisar en Sprint Planning 6.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="27.6" customHeight="1" s="19">
       <c r="A163" s="11" t="inlineStr">
@@ -12760,11 +12820,17 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I163" s="11" t="n"/>
-      <c r="J163" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J163" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML: API_SEL_ML @TIPO 2 (datasets) y GET /sigma-ai/datasets.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="27.6" customHeight="1" s="19">
       <c r="A164" s="11" t="inlineStr">
@@ -12806,7 +12872,11 @@
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
-      <c r="J164" s="12" t="n"/>
+      <c r="J164" s="12" t="inlineStr">
+        <is>
+          <t>Datos reales: datasets FALLA30-20260918-0120 y RUL-20260918-0449 registrados para Hamburgo.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="27.6" customHeight="1" s="19">
       <c r="A165" s="11" t="inlineStr">
@@ -12844,11 +12914,17 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I165" s="11" t="n"/>
-      <c r="J165" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J165" s="12" t="inlineStr">
+        <is>
+          <t>Investigación Azure ML: tarjeta 1 de SIGMA AI › Experimentos (ver muestra, registrar dataset con conteos y SHA-256, CSV).</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="27.6" customHeight="1" s="19">
       <c r="A166" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1159,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="19" min="1" max="1"/>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" s="19">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>HU-067</t>
@@ -5996,6 +5996,81 @@
       <c r="P72" s="12" t="inlineStr">
         <is>
           <t>Solo la tarea de infraestructura (clave de Google Maps). La historia sigue en el Sprint 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" s="19">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>bodeguero</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>que la existencia se lleve por ubicación y por lote, no solo por bodega</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>poder ir directo al estante y saber qué lote tomar antes de que venza</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>App (parte móvil)</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>HU-052, HU-056</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M73" s="11">
+        <f>SUMIF(Tareas!$B$6:$B$600,$A73,Tareas!$F$6:$F$600)</f>
+        <v/>
+      </c>
+      <c r="N73" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>Solo la parte móvil, separada el 22-09-2026 (la historia era «Web y App» y no tenía ninguna tarea Móvil). La parte web se cerró en el Sprint 3 con 4/4 criterios; los puntos quedan allá.</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J514"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="19" min="1" max="1"/>
@@ -6078,8 +6153,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -18290,7 +18363,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" s="19">
       <c r="A286" s="11" t="inlineStr">
         <is>
           <t>T-3934</t>
@@ -28775,6 +28848,52 @@
       <c r="J513" s="12" t="inlineStr">
         <is>
           <t>Servicios externos concentrados en el Sprint 6 (Sprint Review 1, 15-09-2026). Los provee Código Creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" s="19">
+      <c r="A514" s="11" t="inlineStr">
+        <is>
+          <t>T-6306</t>
+        </is>
+      </c>
+      <c r="B514" s="11" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="C514" s="12" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="D514" s="17" t="inlineStr">
+        <is>
+          <t>Pantalla Flutter de existencias del repuesto por estante y lote (consume GET /escaneo con REP-&lt;id&gt; y la sábana de existencias), con el lote que vence antes destacado.</t>
+        </is>
+      </c>
+      <c r="E514" s="11" t="inlineStr">
+        <is>
+          <t>Móvil</t>
+        </is>
+      </c>
+      <c r="F514" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G514" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H514" s="11" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I514" s="11" t="n"/>
+      <c r="J514" s="12" t="inlineStr">
+        <is>
+          <t>Separada de la parte web el 22-09-2026 (cierre del Sprint 3). Lo adelantado en la app antes del Sprint 6 es MVP interno y no cuenta como realizado.</t>
         </is>
       </c>
     </row>
